--- a/offline/variants_data/coldwar/Cold_War.xlsx
+++ b/offline/variants_data/coldwar/Cold_War.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="zones" sheetId="1" state="visible" r:id="rId2"/>
@@ -2263,13 +2263,13 @@
         <v>1</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="G99" s="1" t="n">
         <v>28</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2710,7 +2710,7 @@
       <c r="A27" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>89</v>
       </c>
       <c r="C27" s="1" t="s">
